--- a/DesignTable/Data/Table/Tables/skill.xlsx
+++ b/DesignTable/Data/Table/Tables/skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7835B25A-0F22-4847-8DA6-CBF881C852A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B976050-9EF5-48DD-8A29-42C87A45D172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F9BF89E-1109-4430-8FEA-0CD31C83E41E}"/>
   </bookViews>
@@ -567,7 +567,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="9" Name="skill_맵" RootElement="skill" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="11" Name="skill_맵" RootElement="skill" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -576,70 +576,70 @@
   <autoFilter ref="A1:V6" xr:uid="{853F8BF2-7437-4F67-8640-39E9BF7149BB}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{6EF0E387-D5D4-4ED0-9F12-131C43753272}" uniqueName="unit_Class" name="unit_Class" dataDxfId="22">
-      <xmlColumnPr mapId="9" xpath="/skill/record/unit_Class" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/unit_Class" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C4A7838A-996F-410C-A0DF-57FF01FF7A27}" uniqueName="unit_type" name="unit_type" dataDxfId="21">
-      <xmlColumnPr mapId="9" xpath="/skill/record/unit_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/unit_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{12B86D4F-2F2D-4D15-8954-A779A32D5A56}" uniqueName="skill_Id" name="skill_Id" dataDxfId="20">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{91639917-119A-45ED-8EF7-8A77117DF485}" uniqueName="skill_coolTime" name="skill_coolTime" dataDxfId="19">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_coolTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_coolTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{9BDC73BD-33DC-4401-9D98-23B85612A5F9}" uniqueName="skill_range" name="skill_range" dataDxfId="18">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_range" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_range" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{576A8457-93C8-402F-82FF-A949BC6890DD}" uniqueName="skill_radius" name="skill_radius" dataDxfId="17">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_radius" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_radius" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BCBD11D5-7D29-4195-BB3C-D9039D5FB354}" uniqueName="skill_scale" name="skill_scale" dataDxfId="16">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_scale" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_scale" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{D40AC9FA-E3D5-4DAE-B74F-51530FE3E24E}" uniqueName="skill_buffId" name="skill_buffId" dataDxfId="15">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_buffId" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_buffId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{9B044E9B-92E5-4E1F-BD99-7B57319FC4B3}" uniqueName="skill_type" name="skill_type" dataDxfId="14">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{4B82CBE2-8E95-44C6-B75B-3FB8D2B6E126}" uniqueName="skill_attackType" name="skill_attackType" dataDxfId="13">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_attackType" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_attackType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{22B6DA33-88B3-4278-AA0E-AB7D46B3157B}" uniqueName="skill_contoroll" name="skill_contoroll" dataDxfId="12">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_contoroll" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_contoroll" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{D5C08D3C-1406-4E3B-BFA4-D982E2C29F11}" uniqueName="skill_dash" name="skill_dash" dataDxfId="11">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_dash" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_dash" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{42DDF0FD-A456-4700-B1B3-62ABAACCEB32}" uniqueName="skill_dashSpeed" name="skill_dashSpeed" dataDxfId="10">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_dashSpeed" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_dashSpeed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{F8B7FCB5-4F67-49CD-BB31-80A6D1780DE6}" uniqueName="skill_judgeAni" name="skill_judgeAni" dataDxfId="9">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_judgeAni" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_judgeAni" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{17845948-957A-485B-AF81-16EBA39C286B}" uniqueName="skill_judgeTime" name="skill_judgeTime" dataDxfId="8">
-      <xmlColumnPr mapId="9" xpath="/skill/record/skill_judgeTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/skill_judgeTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{202175A2-302A-47F6-8B21-06758F93C900}" uniqueName="effect_Id" name="effect_Id" dataDxfId="7">
-      <xmlColumnPr mapId="9" xpath="/skill/record/effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{3F7C7D31-C2C2-489B-A70E-F74C7D7E3A4A}" uniqueName="hit_effect_Id" name="hit_effect_Id" dataDxfId="6">
-      <xmlColumnPr mapId="9" xpath="/skill/record/hit_effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/hit_effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{63E47B25-C350-4C31-BF23-D74AC0718CBA}" uniqueName="image_Res" name="image_Res" dataDxfId="5">
-      <xmlColumnPr mapId="9" xpath="/skill/record/image_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/image_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{11615B1C-9C68-4BFF-AB93-023986BF309F}" uniqueName="sound_Res" name="sound_Res" dataDxfId="4">
-      <xmlColumnPr mapId="9" xpath="/skill/record/sound_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/sound_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{F86294E3-CF7F-47CC-BB97-C95A5AAED4B1}" uniqueName="hitSound_Res" name="hitSound_Res" dataDxfId="3">
-      <xmlColumnPr mapId="9" xpath="/skill/record/hitSound_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/hitSound_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{E94EC8F5-940E-479C-8536-E0714E69EFB2}" uniqueName="sound_Ani" name="sound_Ani" dataDxfId="2">
-      <xmlColumnPr mapId="9" xpath="/skill/record/sound_Ani" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/sound_Ani" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="22" xr3:uid="{5D7F94F3-7902-4084-B826-DB209ABF4890}" uniqueName="projectile_Id" name="projectile_Id" dataDxfId="1">
-      <xmlColumnPr mapId="9" xpath="/skill/record/projectile_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/record/projectile_Id" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -651,34 +651,34 @@
   <autoFilter ref="A1:J23" xr:uid="{43A406C0-9967-4ECC-97AB-BA71B93D701D}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{27F4F2F2-5BD9-468B-B369-DC2319E79605}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{89C669FB-CA23-4153-9ED0-299DA35F16EA}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{143AC4C8-50BA-4098-B235-CC5C976AF838}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{19A6A1F8-4A5A-42F4-933F-F637A98BC264}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7AB88B14-0928-41DC-B690-F5A83069A6A6}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{92E43982-C5CC-49AA-BEFF-7D40DF831CEC}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{0AF1C5F9-1BB8-4634-863B-5BDC1918EF8E}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{1C555B1F-285D-44A8-9429-C14BDF4D1497}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{59A7A7C1-C151-4DE1-8C32-98B4EF3FF25A}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{624E087E-77C0-4305-9BA4-E3AEBD91AD06}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="9" xpath="/skill/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="11" xpath="/skill/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/skill.xlsx
+++ b/DesignTable/Data/Table/Tables/skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B976050-9EF5-48DD-8A29-42C87A45D172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9A88586-DEB2-4320-BB15-56447DFC1E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F9BF89E-1109-4430-8FEA-0CD31C83E41E}"/>
   </bookViews>
@@ -567,7 +567,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="11" Name="skill_맵" RootElement="skill" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="13" Name="skill_맵" RootElement="skill" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -576,70 +576,70 @@
   <autoFilter ref="A1:V6" xr:uid="{853F8BF2-7437-4F67-8640-39E9BF7149BB}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{6EF0E387-D5D4-4ED0-9F12-131C43753272}" uniqueName="unit_Class" name="unit_Class" dataDxfId="22">
-      <xmlColumnPr mapId="11" xpath="/skill/record/unit_Class" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/unit_Class" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C4A7838A-996F-410C-A0DF-57FF01FF7A27}" uniqueName="unit_type" name="unit_type" dataDxfId="21">
-      <xmlColumnPr mapId="11" xpath="/skill/record/unit_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/unit_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{12B86D4F-2F2D-4D15-8954-A779A32D5A56}" uniqueName="skill_Id" name="skill_Id" dataDxfId="20">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{91639917-119A-45ED-8EF7-8A77117DF485}" uniqueName="skill_coolTime" name="skill_coolTime" dataDxfId="19">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_coolTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_coolTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{9BDC73BD-33DC-4401-9D98-23B85612A5F9}" uniqueName="skill_range" name="skill_range" dataDxfId="18">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_range" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_range" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{576A8457-93C8-402F-82FF-A949BC6890DD}" uniqueName="skill_radius" name="skill_radius" dataDxfId="17">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_radius" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_radius" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BCBD11D5-7D29-4195-BB3C-D9039D5FB354}" uniqueName="skill_scale" name="skill_scale" dataDxfId="16">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_scale" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_scale" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{D40AC9FA-E3D5-4DAE-B74F-51530FE3E24E}" uniqueName="skill_buffId" name="skill_buffId" dataDxfId="15">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_buffId" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_buffId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{9B044E9B-92E5-4E1F-BD99-7B57319FC4B3}" uniqueName="skill_type" name="skill_type" dataDxfId="14">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{4B82CBE2-8E95-44C6-B75B-3FB8D2B6E126}" uniqueName="skill_attackType" name="skill_attackType" dataDxfId="13">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_attackType" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_attackType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{22B6DA33-88B3-4278-AA0E-AB7D46B3157B}" uniqueName="skill_contoroll" name="skill_contoroll" dataDxfId="12">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_contoroll" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_contoroll" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{D5C08D3C-1406-4E3B-BFA4-D982E2C29F11}" uniqueName="skill_dash" name="skill_dash" dataDxfId="11">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_dash" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_dash" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{42DDF0FD-A456-4700-B1B3-62ABAACCEB32}" uniqueName="skill_dashSpeed" name="skill_dashSpeed" dataDxfId="10">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_dashSpeed" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_dashSpeed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{F8B7FCB5-4F67-49CD-BB31-80A6D1780DE6}" uniqueName="skill_judgeAni" name="skill_judgeAni" dataDxfId="9">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_judgeAni" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_judgeAni" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{17845948-957A-485B-AF81-16EBA39C286B}" uniqueName="skill_judgeTime" name="skill_judgeTime" dataDxfId="8">
-      <xmlColumnPr mapId="11" xpath="/skill/record/skill_judgeTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/skill_judgeTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{202175A2-302A-47F6-8B21-06758F93C900}" uniqueName="effect_Id" name="effect_Id" dataDxfId="7">
-      <xmlColumnPr mapId="11" xpath="/skill/record/effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{3F7C7D31-C2C2-489B-A70E-F74C7D7E3A4A}" uniqueName="hit_effect_Id" name="hit_effect_Id" dataDxfId="6">
-      <xmlColumnPr mapId="11" xpath="/skill/record/hit_effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/hit_effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{63E47B25-C350-4C31-BF23-D74AC0718CBA}" uniqueName="image_Res" name="image_Res" dataDxfId="5">
-      <xmlColumnPr mapId="11" xpath="/skill/record/image_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/image_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{11615B1C-9C68-4BFF-AB93-023986BF309F}" uniqueName="sound_Res" name="sound_Res" dataDxfId="4">
-      <xmlColumnPr mapId="11" xpath="/skill/record/sound_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/sound_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{F86294E3-CF7F-47CC-BB97-C95A5AAED4B1}" uniqueName="hitSound_Res" name="hitSound_Res" dataDxfId="3">
-      <xmlColumnPr mapId="11" xpath="/skill/record/hitSound_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/hitSound_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{E94EC8F5-940E-479C-8536-E0714E69EFB2}" uniqueName="sound_Ani" name="sound_Ani" dataDxfId="2">
-      <xmlColumnPr mapId="11" xpath="/skill/record/sound_Ani" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/sound_Ani" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="22" xr3:uid="{5D7F94F3-7902-4084-B826-DB209ABF4890}" uniqueName="projectile_Id" name="projectile_Id" dataDxfId="1">
-      <xmlColumnPr mapId="11" xpath="/skill/record/projectile_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/record/projectile_Id" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -651,34 +651,34 @@
   <autoFilter ref="A1:J23" xr:uid="{43A406C0-9967-4ECC-97AB-BA71B93D701D}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{27F4F2F2-5BD9-468B-B369-DC2319E79605}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{89C669FB-CA23-4153-9ED0-299DA35F16EA}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{143AC4C8-50BA-4098-B235-CC5C976AF838}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{19A6A1F8-4A5A-42F4-933F-F637A98BC264}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7AB88B14-0928-41DC-B690-F5A83069A6A6}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{92E43982-C5CC-49AA-BEFF-7D40DF831CEC}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{0AF1C5F9-1BB8-4634-863B-5BDC1918EF8E}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{1C555B1F-285D-44A8-9429-C14BDF4D1497}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{59A7A7C1-C151-4DE1-8C32-98B4EF3FF25A}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{624E087E-77C0-4305-9BA4-E3AEBD91AD06}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="11" xpath="/skill/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="13" xpath="/skill/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/skill.xlsx
+++ b/DesignTable/Data/Table/Tables/skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9A88586-DEB2-4320-BB15-56447DFC1E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEE11D45-F1D8-4F7E-9770-8E5BBCB66D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F9BF89E-1109-4430-8FEA-0CD31C83E41E}"/>
   </bookViews>
@@ -567,7 +567,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="13" Name="skill_맵" RootElement="skill" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="14" Name="skill_맵" RootElement="skill" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -576,70 +576,70 @@
   <autoFilter ref="A1:V6" xr:uid="{853F8BF2-7437-4F67-8640-39E9BF7149BB}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{6EF0E387-D5D4-4ED0-9F12-131C43753272}" uniqueName="unit_Class" name="unit_Class" dataDxfId="22">
-      <xmlColumnPr mapId="13" xpath="/skill/record/unit_Class" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/unit_Class" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C4A7838A-996F-410C-A0DF-57FF01FF7A27}" uniqueName="unit_type" name="unit_type" dataDxfId="21">
-      <xmlColumnPr mapId="13" xpath="/skill/record/unit_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/unit_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{12B86D4F-2F2D-4D15-8954-A779A32D5A56}" uniqueName="skill_Id" name="skill_Id" dataDxfId="20">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{91639917-119A-45ED-8EF7-8A77117DF485}" uniqueName="skill_coolTime" name="skill_coolTime" dataDxfId="19">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_coolTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_coolTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{9BDC73BD-33DC-4401-9D98-23B85612A5F9}" uniqueName="skill_range" name="skill_range" dataDxfId="18">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_range" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_range" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{576A8457-93C8-402F-82FF-A949BC6890DD}" uniqueName="skill_radius" name="skill_radius" dataDxfId="17">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_radius" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_radius" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BCBD11D5-7D29-4195-BB3C-D9039D5FB354}" uniqueName="skill_scale" name="skill_scale" dataDxfId="16">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_scale" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_scale" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{D40AC9FA-E3D5-4DAE-B74F-51530FE3E24E}" uniqueName="skill_buffId" name="skill_buffId" dataDxfId="15">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_buffId" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_buffId" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{9B044E9B-92E5-4E1F-BD99-7B57319FC4B3}" uniqueName="skill_type" name="skill_type" dataDxfId="14">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_type" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{4B82CBE2-8E95-44C6-B75B-3FB8D2B6E126}" uniqueName="skill_attackType" name="skill_attackType" dataDxfId="13">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_attackType" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_attackType" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{22B6DA33-88B3-4278-AA0E-AB7D46B3157B}" uniqueName="skill_contoroll" name="skill_contoroll" dataDxfId="12">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_contoroll" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_contoroll" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{D5C08D3C-1406-4E3B-BFA4-D982E2C29F11}" uniqueName="skill_dash" name="skill_dash" dataDxfId="11">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_dash" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_dash" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{42DDF0FD-A456-4700-B1B3-62ABAACCEB32}" uniqueName="skill_dashSpeed" name="skill_dashSpeed" dataDxfId="10">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_dashSpeed" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_dashSpeed" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{F8B7FCB5-4F67-49CD-BB31-80A6D1780DE6}" uniqueName="skill_judgeAni" name="skill_judgeAni" dataDxfId="9">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_judgeAni" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_judgeAni" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{17845948-957A-485B-AF81-16EBA39C286B}" uniqueName="skill_judgeTime" name="skill_judgeTime" dataDxfId="8">
-      <xmlColumnPr mapId="13" xpath="/skill/record/skill_judgeTime" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/skill_judgeTime" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{202175A2-302A-47F6-8B21-06758F93C900}" uniqueName="effect_Id" name="effect_Id" dataDxfId="7">
-      <xmlColumnPr mapId="13" xpath="/skill/record/effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{3F7C7D31-C2C2-489B-A70E-F74C7D7E3A4A}" uniqueName="hit_effect_Id" name="hit_effect_Id" dataDxfId="6">
-      <xmlColumnPr mapId="13" xpath="/skill/record/hit_effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/hit_effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{63E47B25-C350-4C31-BF23-D74AC0718CBA}" uniqueName="image_Res" name="image_Res" dataDxfId="5">
-      <xmlColumnPr mapId="13" xpath="/skill/record/image_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/image_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{11615B1C-9C68-4BFF-AB93-023986BF309F}" uniqueName="sound_Res" name="sound_Res" dataDxfId="4">
-      <xmlColumnPr mapId="13" xpath="/skill/record/sound_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/sound_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{F86294E3-CF7F-47CC-BB97-C95A5AAED4B1}" uniqueName="hitSound_Res" name="hitSound_Res" dataDxfId="3">
-      <xmlColumnPr mapId="13" xpath="/skill/record/hitSound_Res" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/hitSound_Res" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{E94EC8F5-940E-479C-8536-E0714E69EFB2}" uniqueName="sound_Ani" name="sound_Ani" dataDxfId="2">
-      <xmlColumnPr mapId="13" xpath="/skill/record/sound_Ani" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/sound_Ani" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="22" xr3:uid="{5D7F94F3-7902-4084-B826-DB209ABF4890}" uniqueName="projectile_Id" name="projectile_Id" dataDxfId="1">
-      <xmlColumnPr mapId="13" xpath="/skill/record/projectile_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/record/projectile_Id" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -651,34 +651,34 @@
   <autoFilter ref="A1:J23" xr:uid="{43A406C0-9967-4ECC-97AB-BA71B93D701D}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{27F4F2F2-5BD9-468B-B369-DC2319E79605}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{89C669FB-CA23-4153-9ED0-299DA35F16EA}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{143AC4C8-50BA-4098-B235-CC5C976AF838}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{19A6A1F8-4A5A-42F4-933F-F637A98BC264}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{7AB88B14-0928-41DC-B690-F5A83069A6A6}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{92E43982-C5CC-49AA-BEFF-7D40DF831CEC}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{0AF1C5F9-1BB8-4634-863B-5BDC1918EF8E}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{1C555B1F-285D-44A8-9429-C14BDF4D1497}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{59A7A7C1-C151-4DE1-8C32-98B4EF3FF25A}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{624E087E-77C0-4305-9BA4-E3AEBD91AD06}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="13" xpath="/skill/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="14" xpath="/skill/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
